--- a/data/trans_orig/P21D2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49897</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93916</t>
+          <t>92906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44622</t>
+          <t>44861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77023</t>
+          <t>75875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102741</t>
+          <t>104173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156847</t>
+          <t>158419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104730</t>
+          <t>106152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149294</t>
+          <t>150197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86126</t>
+          <t>86109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171445</t>
+          <t>172010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229453</t>
+          <t>227743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26149</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32659</t>
+          <t>31205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76695</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>114114</t>
+          <t>115236</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93741</t>
+          <t>92000</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215718</t>
+          <t>220489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>188572</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>346009</t>
+          <t>339945</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87385</t>
+          <t>87853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125085</t>
+          <t>123953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70722</t>
+          <t>68711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190437</t>
+          <t>191932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>246841</t>
+          <t>246840</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142762</t>
+          <t>153239</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296615</t>
+          <t>297683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,62 +1560,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2436</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>6676</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6779</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73815</t>
+          <t>75127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104666</t>
+          <t>104293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70664</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97549</t>
+          <t>97179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155424</t>
+          <t>156272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193809</t>
+          <t>195804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106455</t>
+          <t>106842</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>137503</t>
+          <t>135933</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>152577</t>
+          <t>151809</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>178484</t>
+          <t>177085</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>265986</t>
+          <t>264608</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>304817</t>
+          <t>305060</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34762</t>
+          <t>33625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>208171</t>
+          <t>209398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85574</t>
+          <t>87671</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112658</t>
+          <t>114380</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,47 +2487,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>206320</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>100019</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>297506</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>24,35%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>35,11%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>206320</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>95095</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>299724</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294447</t>
+          <t>292735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>487614</t>
+          <t>488635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192056</t>
+          <t>189802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222217</t>
+          <t>220632</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513164</t>
+          <t>513400</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>743924</t>
+          <t>738468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38609</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81195</t>
+          <t>81193</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109394</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70049</t>
+          <t>69694</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91338</t>
+          <t>91498</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158123</t>
+          <t>156761</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>194940</t>
+          <t>192941</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118905</t>
+          <t>119794</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147020</t>
+          <t>148023</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>123099</t>
+          <t>122656</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145072</t>
+          <t>145186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246113</t>
+          <t>248976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>284913</t>
+          <t>285683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54569</t>
+          <t>53303</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>73867</t>
+          <t>72999</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>68995</t>
+          <t>68888</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87652</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126785</t>
+          <t>128255</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>155411</t>
+          <t>154686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78173</t>
+          <t>78473</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97707</t>
+          <t>98883</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>92353</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112071</t>
+          <t>111971</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>177714</t>
+          <t>177283</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>206192</t>
+          <t>204541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>59392</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>75992</t>
+          <t>76739</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>91509</t>
+          <t>92288</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>109813</t>
+          <t>110046</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>156671</t>
+          <t>157836</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>181910</t>
+          <t>183026</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>42214</t>
+          <t>41467</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>59142</t>
+          <t>58814</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56415</t>
+          <t>56802</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>74925</t>
+          <t>74612</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>102889</t>
+          <t>102958</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>128169</t>
+          <t>127611</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>536</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>542</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>557</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>345485</t>
+          <t>362189</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>703127</t>
+          <t>704195</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>594684</t>
+          <t>593870</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>797464</t>
+          <t>795992</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>976637</t>
+          <t>968051</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1382742</t>
+          <t>1394349</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>915549</t>
+          <t>914460</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1296494</t>
+          <t>1277927</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>741058</t>
+          <t>743670</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>939514</t>
+          <t>937018</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1777611</t>
+          <t>1763700</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2223700</t>
+          <t>2215510</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>85666</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48944</t>
+          <t>64795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92906</t>
+          <t>110600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>72824</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44861</t>
+          <t>57248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75875</t>
+          <t>89588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>130184</t>
+          <t>158490</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104173</t>
+          <t>131288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158419</t>
+          <t>186559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>129289</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106152</t>
+          <t>92237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150197</t>
+          <t>140002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>79823</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>62952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86109</t>
+          <t>95655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>200126</t>
+          <t>196251</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172010</t>
+          <t>167115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227743</t>
+          <t>220941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>19907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23041</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95401</t>
+          <t>108823</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78360</t>
+          <t>88966</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115236</t>
+          <t>127807</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>145158</t>
+          <t>89201</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92000</t>
+          <t>73064</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220489</t>
+          <t>104542</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240558</t>
+          <t>198023</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>188572</t>
+          <t>175181</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339945</t>
+          <t>225536</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>106251</t>
+          <t>114235</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87853</t>
+          <t>95717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123953</t>
+          <t>134839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>140590</t>
+          <t>153849</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>137230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>191932</t>
+          <t>169709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>246840</t>
+          <t>268084</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>241667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297683</t>
+          <t>289988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>248680</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>248680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>248680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>494181</t>
+          <t>475492</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>494181</t>
+          <t>475492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>494181</t>
+          <t>475492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>108591</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75127</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104293</t>
+          <t>126276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84964</t>
+          <t>99847</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72633</t>
+          <t>85893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97179</t>
+          <t>114363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>174307</t>
+          <t>208438</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156272</t>
+          <t>187810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195804</t>
+          <t>231872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -1976,67 +1976,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122073</t>
+          <t>136186</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106842</t>
+          <t>118905</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135933</t>
+          <t>152408</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>60,36%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>187127</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>172289</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>200835</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>63,08%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>164345</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>151809</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177085</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>63,78%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>323312</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>264608</t>
+          <t>301323</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>305060</t>
+          <t>344736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>912</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>106335</t>
+          <t>121681</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>104721</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>209398</t>
+          <t>137474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>99985</t>
+          <t>114749</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87671</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114380</t>
+          <t>130582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>206320</t>
+          <t>236430</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100019</t>
+          <t>214746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>297506</t>
+          <t>262239</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>407461</t>
+          <t>180337</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292735</t>
+          <t>163593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>488635</t>
+          <t>198990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>207523</t>
+          <t>221618</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>189802</t>
+          <t>206060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220632</t>
+          <t>236673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>614983</t>
+          <t>401955</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513400</t>
+          <t>376600</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>738468</t>
+          <t>424209</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94412</t>
+          <t>104867</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81193</t>
+          <t>88694</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108060</t>
+          <t>119384</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>80376</t>
+          <t>90118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69694</t>
+          <t>77830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91498</t>
+          <t>102205</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>174789</t>
+          <t>194986</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>156761</t>
+          <t>175477</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192941</t>
+          <t>214074</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>133812</t>
+          <t>142603</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119794</t>
+          <t>128225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148023</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>134225</t>
+          <t>148550</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122656</t>
+          <t>136898</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145186</t>
+          <t>161214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>268038</t>
+          <t>291152</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>248976</t>
+          <t>271891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>285683</t>
+          <t>311091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>529</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>29535</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>63841</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>53303</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72999</t>
+          <t>83096</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>78262</t>
+          <t>82259</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>68888</t>
+          <t>72413</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>93097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>142102</t>
+          <t>154285</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>128255</t>
+          <t>140831</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>154686</t>
+          <t>168150</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>88311</t>
+          <t>97602</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78473</t>
+          <t>86759</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>98883</t>
+          <t>110112</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>102466</t>
+          <t>111828</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>92896</t>
+          <t>100781</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>111971</t>
+          <t>122265</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>190776</t>
+          <t>209430</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>177283</t>
+          <t>194737</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>204541</t>
+          <t>223101</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>68136</t>
+          <t>74042</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59392</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>76739</t>
+          <t>83064</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>101206</t>
+          <t>110284</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>92288</t>
+          <t>99138</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>110046</t>
+          <t>119456</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>169343</t>
+          <t>184326</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>157836</t>
+          <t>169588</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>183026</t>
+          <t>198459</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>50070</t>
+          <t>55519</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>41467</t>
+          <t>46497</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58814</t>
+          <t>64597</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>65496</t>
+          <t>72405</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56802</t>
+          <t>62917</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>74612</t>
+          <t>83503</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>115567</t>
+          <t>127924</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>102958</t>
+          <t>113967</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>127611</t>
+          <t>142527</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,22 +4435,22 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>587671</t>
+          <t>675695</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>362189</t>
+          <t>633137</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>704195</t>
+          <t>722066</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>649931</t>
+          <t>659282</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>593870</t>
+          <t>622682</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>795992</t>
+          <t>693736</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1237602</t>
+          <t>1334977</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>968051</t>
+          <t>1269431</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1394349</t>
+          <t>1394617</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1037267</t>
+          <t>842909</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>914460</t>
+          <t>794740</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1277927</t>
+          <t>887212</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>885482</t>
+          <t>975199</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>743670</t>
+          <t>940085</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>937018</t>
+          <t>1011149</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1922749</t>
+          <t>1818108</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1763700</t>
+          <t>1759740</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2215510</t>
+          <t>1878786</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>84305</t>
+          <t>91886</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
